--- a/public/mauxuat.xlsx
+++ b/public/mauxuat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\toanthang\web\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59FA242-2AC8-408C-BD60-572125413611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AD924C-E2FC-46ED-9817-947753211D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0EE1397A-F59D-4B8C-997A-C3CED359D811}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>STT</t>
   </si>
@@ -100,7 +100,7 @@
     <t>- Xuất tại kho: {{chinhanh}}                      -  Địa điểm: Thửa đất số 722, tờ bản đồ số 76, thôn Nam Kỳ, Xã Cuôr Đăng, Tỉnh Đắk Lắk</t>
   </si>
   <si>
-    <t>x</t>
+    <t>X</t>
   </si>
 </sst>
 </file>
@@ -110,7 +110,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;NGÀY &quot;d\ &quot;THÁNG &quot;m\ &quot;NĂM &quot;yyyy"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,18 +142,6 @@
     <font>
       <b/>
       <sz val="13"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -229,6 +217,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -274,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -291,26 +285,47 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -318,48 +333,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -764,13 +752,13 @@
   <sheetData>
     <row r="1" spans="1:23" ht="29" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="4"/>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -791,13 +779,13 @@
     </row>
     <row r="2" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -818,13 +806,13 @@
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="28"/>
+      <c r="C3" s="18"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -844,14 +832,14 @@
       <c r="W3" s="1"/>
     </row>
     <row r="4" spans="1:23" ht="26" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -871,14 +859,14 @@
       <c r="W4" s="1"/>
     </row>
     <row r="5" spans="1:23" ht="23.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -898,14 +886,14 @@
       <c r="W5" s="1"/>
     </row>
     <row r="6" spans="1:23" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -925,12 +913,12 @@
       <c r="W6" s="1"/>
     </row>
     <row r="7" spans="1:23" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -950,14 +938,14 @@
       <c r="W7" s="1"/>
     </row>
     <row r="8" spans="1:23" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -977,14 +965,14 @@
       <c r="W8" s="1"/>
     </row>
     <row r="9" spans="1:23" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -1004,14 +992,14 @@
       <c r="W9" s="1"/>
     </row>
     <row r="10" spans="1:23" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1031,14 +1019,14 @@
       <c r="W10" s="1"/>
     </row>
     <row r="11" spans="1:23" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1058,12 +1046,12 @@
       <c r="W11" s="1"/>
     </row>
     <row r="12" spans="1:23" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -1082,23 +1070,23 @@
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
     </row>
-    <row r="13" spans="1:23" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="19" t="s">
+    <row r="13" spans="1:23" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="F13" s="20"/>
+      <c r="F13" s="27"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1118,14 +1106,14 @@
       <c r="W13" s="1"/>
     </row>
     <row r="14" spans="1:23" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="20"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="7" t="s">
+      <c r="A14" s="27"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="14" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="1"/>
@@ -1148,7 +1136,7 @@
     </row>
     <row r="15" spans="1:23" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
-      <c r="B15" s="14"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
@@ -1171,17 +1159,19 @@
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
     </row>
-    <row r="16" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="9"/>
-      <c r="B16" s="24" t="s">
+    <row r="16" spans="1:23" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="8"/>
+      <c r="B16" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="15"/>
-      <c r="F16" s="16"/>
+      <c r="D16" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1227,14 +1217,14 @@
       <c r="X17" s="1"/>
     </row>
     <row r="18" spans="1:24" ht="23" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1255,8 +1245,8 @@
       <c r="X18" s="1"/>
     </row>
     <row r="19" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="11"/>
+      <c r="E19" s="11"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1277,8 +1267,8 @@
       <c r="X19" s="1"/>
     </row>
     <row r="20" spans="1:24" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="11"/>
-      <c r="E20" s="11"/>
+      <c r="A20" s="10"/>
+      <c r="E20" s="10"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1377,12 +1367,12 @@
       <c r="X23" s="1"/>
     </row>
     <row r="24" spans="1:24" ht="15" x14ac:dyDescent="0.35">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -1430,11 +1420,11 @@
     </row>
     <row r="26" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -26623,7 +26613,17 @@
       <c r="X994" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="B1:F1"/>
@@ -26634,17 +26634,6 @@
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.2" top="0.25" bottom="0.75" header="0.05" footer="0"/>
   <pageSetup paperSize="250" scale="61" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
